--- a/InputData/indst/SYIEUEFbIPaF/Start Year Indst Eqpt Unit E Factor by Indst Proc and Fuel.xlsx
+++ b/InputData/indst/SYIEUEFbIPaF/Start Year Indst Eqpt Unit E Factor by Indst Proc and Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\SYIEUEFbIPaF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E828D518-C7AF-4DB9-921B-A6E9A6DA3B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583D8F56-BA9A-4554-A7B4-97607820984D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
+    <workbookView xWindow="1410" yWindow="1520" windowWidth="17790" windowHeight="9120" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,8 +22,200 @@
     <sheet name="High Temp" sheetId="12" r:id="rId7"/>
     <sheet name="Cooling" sheetId="11" r:id="rId8"/>
     <sheet name="Electrochemical" sheetId="14" r:id="rId9"/>
-    <sheet name="SYIEUEFbIPaF" sheetId="2" r:id="rId10"/>
+    <sheet name="Other" sheetId="15" r:id="rId10"/>
+    <sheet name="References" sheetId="16" r:id="rId11"/>
+    <sheet name="SYIEUEFbIPaF" sheetId="2" r:id="rId12"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
+    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="base.year">#REF!</definedName>
+    <definedName name="CH4_to_CO2e">'[2]Cross-Page Data'!$C$12</definedName>
+    <definedName name="CH4GWP">#REF!</definedName>
+    <definedName name="coal.past">#REF!</definedName>
+    <definedName name="Constants.Density.Diesel">#REF!</definedName>
+    <definedName name="Constants.Density.Ethanol">#REF!</definedName>
+    <definedName name="Constants.Density.JetFuel">#REF!</definedName>
+    <definedName name="Constants.Density.MotorSpirit">#REF!</definedName>
+    <definedName name="Conversion.to.average.power">#REF!</definedName>
+    <definedName name="Conversion.water.L">#REF!</definedName>
+    <definedName name="Conversion.water.units">#REF!</definedName>
+    <definedName name="Conversions.Area.m2">#REF!</definedName>
+    <definedName name="Conversions.Area.Units">#REF!</definedName>
+    <definedName name="Conversions.Energy.Joules">#REF!</definedName>
+    <definedName name="Conversions.Energy.Units">#REF!</definedName>
+    <definedName name="Conversions.Money.GBP">#REF!</definedName>
+    <definedName name="Conversions.Money.Units">#REF!</definedName>
+    <definedName name="Conversions.Power.Units">#REF!</definedName>
+    <definedName name="Conversions.Power.Watts">#REF!</definedName>
+    <definedName name="Cost.Capital.Scenario">#REF!</definedName>
+    <definedName name="Cost.Finance.Scenario">#REF!</definedName>
+    <definedName name="Cost.Fuel.Scenario">#REF!</definedName>
+    <definedName name="Cost.Infrastructure.Scenario">#REF!</definedName>
+    <definedName name="cpi_2010to2012">#REF!</definedName>
+    <definedName name="cpi_2013to2012">#REF!</definedName>
+    <definedName name="cpi_2014to2012">#REF!</definedName>
+    <definedName name="cpi_2016to2012">#REF!</definedName>
+    <definedName name="csp.capacity">#REF!</definedName>
+    <definedName name="D">#REF!</definedName>
+    <definedName name="discount_factors">#REF!</definedName>
+    <definedName name="EF.BlastFurnaceGas.CO2">#REF!</definedName>
+    <definedName name="EF.Diesel.CH4">#REF!</definedName>
+    <definedName name="EF.Diesel.CO2">#REF!</definedName>
+    <definedName name="EF.Diesel.N2O">#REF!</definedName>
+    <definedName name="EF.IndustrialCoal.CH4">#REF!</definedName>
+    <definedName name="EF.IndustrialCoal.CO2">#REF!</definedName>
+    <definedName name="EF.IndustrialCoal.N2O">#REF!</definedName>
+    <definedName name="EF.NaturalGas.CH4">#REF!</definedName>
+    <definedName name="EF.NaturalGas.CO2">#REF!</definedName>
+    <definedName name="EF.NaturalGas.N2O">#REF!</definedName>
+    <definedName name="GBP">#REF!</definedName>
+    <definedName name="gigwatts_to_megawatts">[3]About!$A$31</definedName>
+    <definedName name="growth.scenario">#REF!</definedName>
+    <definedName name="GWP.CH4">#REF!</definedName>
+    <definedName name="GWP.N2O">#REF!</definedName>
+    <definedName name="GWPCH4">#REF!</definedName>
+    <definedName name="GWPN2O">#REF!</definedName>
+    <definedName name="h">#REF!</definedName>
+    <definedName name="I.01">#REF!</definedName>
+    <definedName name="I.a.scenario">#REF!</definedName>
+    <definedName name="I.b.scenario">#REF!</definedName>
+    <definedName name="I.b.scenario.efficiency">#REF!</definedName>
+    <definedName name="I.c.scenario">#REF!</definedName>
+    <definedName name="I.c.scenario.fuelmix">#REF!</definedName>
+    <definedName name="II.scenario">#REF!</definedName>
+    <definedName name="III.scenario">#REF!</definedName>
+    <definedName name="input.choice">#REF!</definedName>
+    <definedName name="INR">#REF!</definedName>
+    <definedName name="INRb">#REF!</definedName>
+    <definedName name="INRCr">#REF!</definedName>
+    <definedName name="INRLac">#REF!</definedName>
+    <definedName name="INRt">#REF!</definedName>
+    <definedName name="IV.a.scenario">#REF!</definedName>
+    <definedName name="IV.b.scenario">#REF!</definedName>
+    <definedName name="IV.c.1.scenario">#REF!</definedName>
+    <definedName name="iv.c.2.scenario">#REF!</definedName>
+    <definedName name="IV.d.scenario">#REF!</definedName>
+    <definedName name="IV.e.scenario">#REF!</definedName>
+    <definedName name="IV.f.scenario">#REF!</definedName>
+    <definedName name="IX.a.scenario">#REF!</definedName>
+    <definedName name="MGBP">#REF!</definedName>
+    <definedName name="Minesize.xv.b">#REF!</definedName>
+    <definedName name="N2O_to_CO2e">'[2]Cross-Page Data'!$C$13</definedName>
+    <definedName name="N2OGWP">#REF!</definedName>
+    <definedName name="nuclear.past">#REF!</definedName>
+    <definedName name="plantsize.I.b">#REF!</definedName>
+    <definedName name="Plantsize.II">#REF!</definedName>
+    <definedName name="Plantsize.III">#REF!</definedName>
+    <definedName name="plantsize.iv.a">#REF!</definedName>
+    <definedName name="plantsize.iv.b">#REF!</definedName>
+    <definedName name="Plantsize.iv.c.1">#REF!</definedName>
+    <definedName name="plantsize.iv.c.2">#REF!</definedName>
+    <definedName name="plantsize.iv.d">#REF!</definedName>
+    <definedName name="predefined.scenario">#REF!</definedName>
+    <definedName name="Preferences.AreaUnits">#REF!</definedName>
+    <definedName name="preferences.energyunits">#REF!</definedName>
+    <definedName name="Preferences.moneyunits">#REF!</definedName>
+    <definedName name="Preferences.PowerUnits">#REF!</definedName>
+    <definedName name="Preferences.Unit.Energy">#REF!</definedName>
+    <definedName name="Preferences.Unit.Power">#REF!</definedName>
+    <definedName name="Preferences.waterunit">#REF!</definedName>
+    <definedName name="Print_Area_MI">#REF!</definedName>
+    <definedName name="Reliability.scenario">#REF!</definedName>
+    <definedName name="small_hydro.capacity">#REF!</definedName>
+    <definedName name="target.year">#REF!</definedName>
+    <definedName name="Unit.acre">#REF!</definedName>
+    <definedName name="unit.bcm">#REF!</definedName>
+    <definedName name="Unit.boe">#REF!</definedName>
+    <definedName name="Unit.calorie">#REF!</definedName>
+    <definedName name="Unit.day">#REF!</definedName>
+    <definedName name="Unit.GJ">#REF!</definedName>
+    <definedName name="Unit.GW">#REF!</definedName>
+    <definedName name="Unit.GWh">#REF!</definedName>
+    <definedName name="Unit.ha">#REF!</definedName>
+    <definedName name="Unit.hour">#REF!</definedName>
+    <definedName name="Unit.J">#REF!</definedName>
+    <definedName name="unit.kcng">#REF!</definedName>
+    <definedName name="unit.kgb">#REF!</definedName>
+    <definedName name="unit.kgce">#REF!</definedName>
+    <definedName name="unit.kghe">#REF!</definedName>
+    <definedName name="unit.kglpge">#REF!</definedName>
+    <definedName name="Unit.km2">#REF!</definedName>
+    <definedName name="Unit.kW">#REF!</definedName>
+    <definedName name="Unit.kWh">#REF!</definedName>
+    <definedName name="unit.L">#REF!</definedName>
+    <definedName name="unit.latfe">#REF!</definedName>
+    <definedName name="unit.lcng">#REF!</definedName>
+    <definedName name="unit.lde">#REF!</definedName>
+    <definedName name="unit.lke">#REF!</definedName>
+    <definedName name="unit.lpe">#REF!</definedName>
+    <definedName name="Unit.m2">#REF!</definedName>
+    <definedName name="Unit.m3">#REF!</definedName>
+    <definedName name="unit.MCM">#REF!</definedName>
+    <definedName name="Unit.minute">#REF!</definedName>
+    <definedName name="Unit.MJ">#REF!</definedName>
+    <definedName name="unit.mmbtu">#REF!</definedName>
+    <definedName name="unit.mmscm">#REF!</definedName>
+    <definedName name="unit.mtcce">#REF!</definedName>
+    <definedName name="Unit.Mtce">#REF!</definedName>
+    <definedName name="unit.mtde">#REF!</definedName>
+    <definedName name="unit.mticce">#REF!</definedName>
+    <definedName name="unit.mtice">#REF!</definedName>
+    <definedName name="unit.mtle">#REF!</definedName>
+    <definedName name="Unit.Mtoe">#REF!</definedName>
+    <definedName name="Unit.MW">#REF!</definedName>
+    <definedName name="Unit.MWh">#REF!</definedName>
+    <definedName name="Unit.PJ">#REF!</definedName>
+    <definedName name="unit.scm">#REF!</definedName>
+    <definedName name="unit.scmb">#REF!</definedName>
+    <definedName name="unit.tce">#REF!</definedName>
+    <definedName name="unit.ticce">#REF!</definedName>
+    <definedName name="unit.tice">#REF!</definedName>
+    <definedName name="Unit.TJ">#REF!</definedName>
+    <definedName name="Unit.toe">#REF!</definedName>
+    <definedName name="Unit.TWh">#REF!</definedName>
+    <definedName name="Unit.W">#REF!</definedName>
+    <definedName name="Unit.year">#REF!</definedName>
+    <definedName name="unit_conv">[4]About!$A$123</definedName>
+    <definedName name="USD_Bn">#REF!</definedName>
+    <definedName name="USD_mn">#REF!</definedName>
+    <definedName name="USD2012_">#REF!</definedName>
+    <definedName name="v.a.scenario">#REF!</definedName>
+    <definedName name="V.b.scenario">#REF!</definedName>
+    <definedName name="V.c.scenario">#REF!</definedName>
+    <definedName name="VI.a.scenario">#REF!</definedName>
+    <definedName name="VII.a.scenario">#REF!</definedName>
+    <definedName name="VII.b.scenario">#REF!</definedName>
+    <definedName name="X.a.economy">#REF!</definedName>
+    <definedName name="X.a.epi">#REF!</definedName>
+    <definedName name="X.a.floorspace">#REF!</definedName>
+    <definedName name="X.b.ac">#REF!</definedName>
+    <definedName name="X.b.ecbc">#REF!</definedName>
+    <definedName name="x.b.floorspace">#REF!</definedName>
+    <definedName name="XI.cement.fuel">#REF!</definedName>
+    <definedName name="XI.fuelmix">#REF!</definedName>
+    <definedName name="XI.scenario">#REF!</definedName>
+    <definedName name="XI.steel.fuel">#REF!</definedName>
+    <definedName name="XII.a.scenario">#REF!</definedName>
+    <definedName name="XII.a.scenario.EVs">#REF!</definedName>
+    <definedName name="XII.a.scenario.mode">#REF!</definedName>
+    <definedName name="XII.a.scenario.pub_pri">#REF!</definedName>
+    <definedName name="XII.b.mode">#REF!</definedName>
+    <definedName name="XII.b.scenario">#REF!</definedName>
+    <definedName name="XIII.a.chulhas">#REF!</definedName>
+    <definedName name="XIII.a.scenario.fuelsplit">#REF!</definedName>
+    <definedName name="XIII.b">#REF!</definedName>
+    <definedName name="XIV.scenario">#REF!</definedName>
+    <definedName name="XIV.scenario.fuelsplit">#REF!</definedName>
+    <definedName name="xv.a.scenario">#REF!</definedName>
+    <definedName name="xv.b.scenario">#REF!</definedName>
+    <definedName name="XV.c.scenario">#REF!</definedName>
+    <definedName name="xvi.scenario.fuelsplit">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -67,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="249">
   <si>
     <t>Source:</t>
   </si>
@@ -618,6 +810,248 @@
   </si>
   <si>
     <t>Diesel generator / NG combustion turbine</t>
+  </si>
+  <si>
+    <t>Ag tractors (mobile equipment)</t>
+  </si>
+  <si>
+    <t>Tractor</t>
+  </si>
+  <si>
+    <t>η</t>
+  </si>
+  <si>
+    <t>nom P [kW]</t>
+  </si>
+  <si>
+    <t>nom w [rpm]</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ref 19 // </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>open circles are added via post processing and represent the weighted</t>
+    </r>
+  </si>
+  <si>
+    <t>unkn.</t>
+  </si>
+  <si>
+    <t>average load &amp; engine speeds from ref 20 scaled by nominal engine speeds</t>
+  </si>
+  <si>
+    <t>4WD / MFWD</t>
+  </si>
+  <si>
+    <t>245/127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric </t>
+  </si>
+  <si>
+    <t>PM Electric Motor</t>
+  </si>
+  <si>
+    <t>150 (overload)</t>
+  </si>
+  <si>
+    <t>charging adjusted</t>
+  </si>
+  <si>
+    <t>22,25</t>
+  </si>
+  <si>
+    <t>Custom autonomous</t>
+  </si>
+  <si>
+    <t>Simulated autonomous</t>
+  </si>
+  <si>
+    <t>Reduction in fuel use</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ref 21 // </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>open circles are added via post processing and represent the weighted</t>
+    </r>
+  </si>
+  <si>
+    <t>Ref 20</t>
+  </si>
+  <si>
+    <t>(from figure)</t>
+  </si>
+  <si>
+    <t>Tables 2-5</t>
+  </si>
+  <si>
+    <t>weighted values</t>
+  </si>
+  <si>
+    <t>max t at speed</t>
+  </si>
+  <si>
+    <t>load (fig 16)</t>
+  </si>
+  <si>
+    <t>speed on fig 2</t>
+  </si>
+  <si>
+    <t>speed on fig 14</t>
+  </si>
+  <si>
+    <t>torque on fig 2</t>
+  </si>
+  <si>
+    <t>torque on fig 14</t>
+  </si>
+  <si>
+    <t>% of total field time</t>
+  </si>
+  <si>
+    <t>weighted average torque %</t>
+  </si>
+  <si>
+    <t>weighted average engine speed</t>
+  </si>
+  <si>
+    <t>weighted-average torque</t>
+  </si>
+  <si>
+    <t>weighted-average engine speed</t>
+  </si>
+  <si>
+    <t>Field operation</t>
+  </si>
+  <si>
+    <t>t (%)</t>
+  </si>
+  <si>
+    <t>w (s^-1)</t>
+  </si>
+  <si>
+    <t>TS-I</t>
+  </si>
+  <si>
+    <t>TS-II</t>
+  </si>
+  <si>
+    <t>TS-III</t>
+  </si>
+  <si>
+    <t>NH3 application</t>
+  </si>
+  <si>
+    <t>Field cultivation</t>
+  </si>
+  <si>
+    <t>Corn planting</t>
+  </si>
+  <si>
+    <t>Reference Number</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Page or Table</t>
+  </si>
+  <si>
+    <t>D. Friso</t>
+  </si>
+  <si>
+    <t>Brake Thermal Efficiency and BSFC of Diesel  Engines: Mathematical Modeling and Comparison  between Diesel Oil and Biodiesel Fueling</t>
+  </si>
+  <si>
+    <t>https://www.m-hikari.com/ams/ams-2014/ams-129-132-2014/frisoAMS129-132-2014-1.pdf</t>
+  </si>
+  <si>
+    <t>S. Pitla, J.D. Luck, J. Werner, N. Line, S.A. Shearer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-field fuel use and load states of agricultural field machinery </t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0168169916000041</t>
+  </si>
+  <si>
+    <t>D. Troncon, L. Alberti</t>
+  </si>
+  <si>
+    <t>Case of Study of the Electrification of a Tractor: Electric Motor Performance Requirements and Design</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/1996-1073/13/9/2197</t>
+  </si>
+  <si>
+    <t>Z. Shao, S. Anup</t>
+  </si>
+  <si>
+    <t>Incentives for electrifying agricultural tractors in India</t>
+  </si>
+  <si>
+    <t>https://theicct.org/publication/india-hvs-evs-incentives-elec-tractors-india-oct22/</t>
+  </si>
+  <si>
+    <t>O. Lagnelov et al.</t>
+  </si>
+  <si>
+    <t>Cost analysis of autonomous battery electric field tractors in agriculture</t>
+  </si>
+  <si>
+    <t>https://pub.epsilon.slu.se/id/document/20368600</t>
+  </si>
+  <si>
+    <t>J. Engstrom and O. Lagnelov</t>
+  </si>
+  <si>
+    <t>An Autonomous Electric Powered Tractor—Simulation of All Operations on a Swedish Dairy Farm</t>
+  </si>
+  <si>
+    <t>https://www.davidpublisher.com/Public/uploads/Contribute/5ba1b8c2036b0.pdf</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy</t>
+  </si>
+  <si>
+    <t>Where the Energy Goes: Electric Cars</t>
+  </si>
+  <si>
+    <t>https://www.fueleconomy.gov/feg/atv-ev.shtml</t>
   </si>
 </sst>
 </file>
@@ -686,7 +1120,7 @@
       <name val="Segoeui"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -717,6 +1151,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -732,7 +1172,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -765,6 +1205,26 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1254,6 +1714,335 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>216087</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>164826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCE30D4C-512C-469E-94E6-11987F13273C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6407150" y="736600"/>
+          <a:ext cx="4483287" cy="2190476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>122869</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>160057</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC863150-523E-4012-902A-13C2F61B04EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6407150" y="3683000"/>
+          <a:ext cx="2561269" cy="2185707"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="EIA MECS Table 5.2"/>
+      <sheetName val="Med-High Temp Heat"/>
+      <sheetName val="Low Temp Heat"/>
+      <sheetName val="Cooling"/>
+      <sheetName val="Other"/>
+      <sheetName val="Efficiencies"/>
+      <sheetName val="Temperature Breakdown"/>
+      <sheetName val="References"/>
+      <sheetName val="Mapping"/>
+      <sheetName val="PIFURfE"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Cross-Page Data"/>
+      <sheetName val="Non-Energy FF CO2 Emissions"/>
+      <sheetName val="Cement CO2 Emissions"/>
+      <sheetName val="Iron and Steel"/>
+      <sheetName val="Coal Mining"/>
+      <sheetName val="Natural Gas Systems"/>
+      <sheetName val="Petroleum Systems"/>
+      <sheetName val="Chem - HCFC 22 Production"/>
+      <sheetName val="Chem - ODS"/>
+      <sheetName val="Other - Aluminum"/>
+      <sheetName val="Other - Magnesium"/>
+      <sheetName val="Other - Semiconductor Mfg"/>
+      <sheetName val="Other - Elec Trans and Dist"/>
+      <sheetName val="Agriculture - EF &amp; Manure Mgmt"/>
+      <sheetName val="Agriculture - Rice Cultivation"/>
+      <sheetName val="Agriculture - Soil Mgmt"/>
+      <sheetName val="Waste - Landfills"/>
+      <sheetName val="Waste - Water Treatment"/>
+      <sheetName val="Other Industrial Processes"/>
+      <sheetName val="Combined Data"/>
+      <sheetName val="BPEiC-CO2"/>
+      <sheetName val="BPEiC-CH4"/>
+      <sheetName val="BPEiC-N2O"/>
+      <sheetName val="BPEiC-F-gases"/>
+      <sheetName val="EPA (2017) Table A3.6-1"/>
+      <sheetName val="EPA (2017) Table A3.6-7"/>
+      <sheetName val="EPA (2017) Table A3.6-10"/>
+      <sheetName val="AEO 2017_Table 6"/>
+      <sheetName val="AEO 2017_Table 11"/>
+      <sheetName val="AEO 2017_Table 13"/>
+      <sheetName val="AEO 2017_Table 15"/>
+      <sheetName val="AEO 2017_Table 19"/>
+      <sheetName val="AEO 2017_Table 20"/>
+      <sheetName val="AEO 2017_Table 24"/>
+      <sheetName val="AEO 2017_Table 62"/>
+      <sheetName val="AEO 2016_Table 6"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="C12">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>265</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Transport Refrigeration</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
+      <sheetData sheetId="32"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="2035 Report Deployment"/>
+      <sheetName val="2035 Report Data"/>
+      <sheetName val="EPS Output"/>
+      <sheetName val="AEO Table 9"/>
+      <sheetName val="AEO Table 9 (2019)"/>
+      <sheetName val="AEO Table 16"/>
+      <sheetName val="BGBSC"/>
+      <sheetName val="PAGBSC"/>
+      <sheetName val="SYGBSC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="31">
+          <cell r="A31">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="Country Selector"/>
+      <sheetName val="Multipliers and Adjustments"/>
+      <sheetName val="EPA Data"/>
+      <sheetName val="Tech to Policy Mapping"/>
+      <sheetName val="SNAP Adjustment"/>
+      <sheetName val="Cement Data"/>
+      <sheetName val="Data Check"/>
+      <sheetName val="PERAC-cement"/>
+      <sheetName val="PERAC-ngps-mthncptr"/>
+      <sheetName val="PERAC-ngps-mthndstr"/>
+      <sheetName val="PERAC-fgassubstitution"/>
+      <sheetName val="PERAC-fgasdestruction"/>
+      <sheetName val="PERAC-fgasrecovery"/>
+      <sheetName val="PERAC-inspctmaintretrofit"/>
+      <sheetName val="PERAC-coalmining-mthncptr"/>
+      <sheetName val="PERAC-coalmining-mthndstr"/>
+      <sheetName val="PERAC-waste-mthncptr"/>
+      <sheetName val="PERAC-waste-mthndstr"/>
+      <sheetName val="PERAC-cropsrice"/>
+      <sheetName val="PERAC-livestock"/>
+      <sheetName val="PERAC-MCD"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="123">
+          <cell r="A123">
+            <v>1000000000000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1825,6 +2614,891 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2927FF-B932-47A4-981F-D26F3F21BFFF}">
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="27">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="C4" s="12">
+        <f>1/B4</f>
+        <v>3.3003300330033003</v>
+      </c>
+      <c r="D4">
+        <v>58.8</v>
+      </c>
+      <c r="E4">
+        <v>2500</v>
+      </c>
+      <c r="F4">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="27">
+        <f>AVERAGE(0.35,0.305,0.266)</f>
+        <v>0.307</v>
+      </c>
+      <c r="C5" s="12">
+        <f>1/B5</f>
+        <v>3.2573289902280131</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5">
+        <v>2100</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9">
+        <f>AVERAGE(0.836,0.885,0.905)</f>
+        <v>0.87533333333333341</v>
+      </c>
+      <c r="C9">
+        <f>1/B9</f>
+        <v>1.1424219345011424</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9">
+        <v>2600</v>
+      </c>
+      <c r="F9">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10">
+        <f>B9*(1-AVERAGE(0.1,0.15))</f>
+        <v>0.76591666666666669</v>
+      </c>
+      <c r="C10">
+        <f>1/B10</f>
+        <v>1.3056250680013055</v>
+      </c>
+      <c r="D10" s="28"/>
+      <c r="F10" s="28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11">
+        <f>1/C11</f>
+        <v>0.64890826648064182</v>
+      </c>
+      <c r="C11">
+        <f>AVERAGE(C4:C5)*(1-AVERAGE(0.52,0.54))</f>
+        <v>1.5410498704593585</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12">
+        <f>1/C12</f>
+        <v>0.72615925058548003</v>
+      </c>
+      <c r="C12">
+        <f>AVERAGE(C4:C5)*(1-AVERAGE(0.58))</f>
+        <v>1.3771083948785758</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="F12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="B15" s="14">
+        <f>(AVERAGE(C4:C5)-AVERAGE(C10:C12))/AVERAGE(C4:C5)</f>
+        <v>0.57060049240377109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="25"/>
+      <c r="B16" s="14"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="2"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" t="s">
+        <v>200</v>
+      </c>
+      <c r="B34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D34" t="s">
+        <v>202</v>
+      </c>
+      <c r="E34" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" t="s">
+        <v>204</v>
+      </c>
+      <c r="G34" t="s">
+        <v>205</v>
+      </c>
+      <c r="H34" t="s">
+        <v>206</v>
+      </c>
+      <c r="I34" t="s">
+        <v>207</v>
+      </c>
+      <c r="J34" t="s">
+        <v>208</v>
+      </c>
+      <c r="M34" t="s">
+        <v>209</v>
+      </c>
+      <c r="P34" t="s">
+        <v>210</v>
+      </c>
+      <c r="S34" t="s">
+        <v>211</v>
+      </c>
+      <c r="T34" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" t="s">
+        <v>215</v>
+      </c>
+      <c r="J35" t="s">
+        <v>216</v>
+      </c>
+      <c r="K35" t="s">
+        <v>217</v>
+      </c>
+      <c r="L35" t="s">
+        <v>218</v>
+      </c>
+      <c r="M35" t="s">
+        <v>216</v>
+      </c>
+      <c r="N35" t="s">
+        <v>217</v>
+      </c>
+      <c r="O35" t="s">
+        <v>218</v>
+      </c>
+      <c r="P35" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>217</v>
+      </c>
+      <c r="R35" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" s="18">
+        <f>AVERAGE(S36:S37)</f>
+        <v>41.68</v>
+      </c>
+      <c r="C36" s="18">
+        <f>AVERAGE(T36:T37)</f>
+        <v>1840.7550000000001</v>
+      </c>
+      <c r="D36" s="18">
+        <v>213</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="F36" s="18">
+        <f>C36*$E$4/$E$5*2*PI()/60</f>
+        <v>229.48025337534443</v>
+      </c>
+      <c r="G36" s="18">
+        <f>C36*$E$9/$E$5</f>
+        <v>2279.0300000000002</v>
+      </c>
+      <c r="H36" s="18">
+        <f>E36*D36</f>
+        <v>80.94</v>
+      </c>
+      <c r="I36" s="18">
+        <f>150*E36</f>
+        <v>57</v>
+      </c>
+      <c r="J36">
+        <v>8</v>
+      </c>
+      <c r="K36">
+        <v>22</v>
+      </c>
+      <c r="L36">
+        <v>70</v>
+      </c>
+      <c r="M36">
+        <v>8</v>
+      </c>
+      <c r="N36">
+        <v>23</v>
+      </c>
+      <c r="O36">
+        <v>52</v>
+      </c>
+      <c r="P36">
+        <v>884</v>
+      </c>
+      <c r="Q36">
+        <v>1711</v>
+      </c>
+      <c r="R36">
+        <v>2009</v>
+      </c>
+      <c r="S36">
+        <f>SUMPRODUCT(J36:L36,M36:O36)/SUM(J36:L36)</f>
+        <v>42.1</v>
+      </c>
+      <c r="T36">
+        <f>SUMPRODUCT(P36:R36,J36:L36)/SUM(J36:L36)</f>
+        <v>1853.44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="3"/>
+      <c r="J37">
+        <v>8</v>
+      </c>
+      <c r="K37">
+        <v>21</v>
+      </c>
+      <c r="L37">
+        <v>71</v>
+      </c>
+      <c r="M37">
+        <v>9</v>
+      </c>
+      <c r="N37">
+        <v>24</v>
+      </c>
+      <c r="O37">
+        <v>50</v>
+      </c>
+      <c r="P37">
+        <v>955</v>
+      </c>
+      <c r="Q37">
+        <v>1718</v>
+      </c>
+      <c r="R37">
+        <v>1959</v>
+      </c>
+      <c r="S37">
+        <f t="shared" ref="S37:S43" si="0">SUMPRODUCT(J37:L37,M37:O37)/SUM(J37:L37)</f>
+        <v>41.26</v>
+      </c>
+      <c r="T37">
+        <f t="shared" ref="T37:T43" si="1">SUMPRODUCT(P37:R37,J37:L37)/SUM(J37:L37)</f>
+        <v>1828.07</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
+      <c r="A38" t="s">
+        <v>220</v>
+      </c>
+      <c r="B38" s="18">
+        <f>AVERAGE(S38:S40)</f>
+        <v>55.79</v>
+      </c>
+      <c r="C38" s="18">
+        <f>AVERAGE(T38:T39)</f>
+        <v>1791.8899999999999</v>
+      </c>
+      <c r="D38" s="18">
+        <v>215</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="F38" s="18">
+        <f>C38*$E$4/$E$5*2*PI()/60</f>
+        <v>223.3884309540085</v>
+      </c>
+      <c r="G38" s="18">
+        <f>C38*$E$9/$E$5</f>
+        <v>2218.5304761904763</v>
+      </c>
+      <c r="H38" s="18">
+        <f>E38*D38</f>
+        <v>103.2</v>
+      </c>
+      <c r="I38" s="18">
+        <f>150*E38</f>
+        <v>72</v>
+      </c>
+      <c r="J38">
+        <v>4</v>
+      </c>
+      <c r="K38">
+        <v>25</v>
+      </c>
+      <c r="L38">
+        <v>71</v>
+      </c>
+      <c r="M38">
+        <v>13</v>
+      </c>
+      <c r="N38">
+        <v>33</v>
+      </c>
+      <c r="O38">
+        <v>66</v>
+      </c>
+      <c r="P38">
+        <v>1455</v>
+      </c>
+      <c r="Q38">
+        <v>1568</v>
+      </c>
+      <c r="R38">
+        <v>1767</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="0"/>
+        <v>55.63</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="1"/>
+        <v>1704.77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="3"/>
+      <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39">
+        <v>27</v>
+      </c>
+      <c r="L39">
+        <v>70</v>
+      </c>
+      <c r="M39">
+        <v>13</v>
+      </c>
+      <c r="N39">
+        <v>35</v>
+      </c>
+      <c r="O39">
+        <v>68</v>
+      </c>
+      <c r="P39">
+        <v>1543</v>
+      </c>
+      <c r="Q39">
+        <v>1696</v>
+      </c>
+      <c r="R39">
+        <v>1964</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="0"/>
+        <v>57.44</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="1"/>
+        <v>1879.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="3"/>
+      <c r="J40">
+        <v>3</v>
+      </c>
+      <c r="K40">
+        <v>24</v>
+      </c>
+      <c r="L40">
+        <v>73</v>
+      </c>
+      <c r="M40">
+        <v>13</v>
+      </c>
+      <c r="N40">
+        <v>33</v>
+      </c>
+      <c r="O40">
+        <v>63</v>
+      </c>
+      <c r="P40">
+        <v>905</v>
+      </c>
+      <c r="Q40">
+        <v>1541</v>
+      </c>
+      <c r="R40">
+        <v>1827</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="0"/>
+        <v>54.3</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="1"/>
+        <v>1730.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="A41" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" s="18">
+        <f>AVERAGE(S41:S43)</f>
+        <v>73.423333333333332</v>
+      </c>
+      <c r="C41" s="18">
+        <f>AVERAGE(T41:T42)</f>
+        <v>1395.97</v>
+      </c>
+      <c r="D41" s="18">
+        <v>220</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.59</v>
+      </c>
+      <c r="F41" s="18">
+        <f>C41*$E$4/$E$5*2*PI()/60</f>
+        <v>174.0305197076089</v>
+      </c>
+      <c r="G41" s="18">
+        <f>C41*$E$9/$E$5</f>
+        <v>1728.3438095238096</v>
+      </c>
+      <c r="H41" s="18">
+        <f>E41*D41</f>
+        <v>129.79999999999998</v>
+      </c>
+      <c r="I41" s="18">
+        <f>150*E41</f>
+        <v>88.5</v>
+      </c>
+      <c r="J41">
+        <v>41</v>
+      </c>
+      <c r="K41">
+        <v>59</v>
+      </c>
+      <c r="M41">
+        <v>37</v>
+      </c>
+      <c r="N41">
+        <v>76</v>
+      </c>
+      <c r="P41">
+        <v>904</v>
+      </c>
+      <c r="Q41">
+        <v>1514</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="0"/>
+        <v>60.01</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="1"/>
+        <v>1263.9000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="J42">
+        <v>4</v>
+      </c>
+      <c r="K42">
+        <v>96</v>
+      </c>
+      <c r="M42">
+        <v>36</v>
+      </c>
+      <c r="N42">
+        <v>81</v>
+      </c>
+      <c r="P42">
+        <v>1433</v>
+      </c>
+      <c r="Q42">
+        <v>1532</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="0"/>
+        <v>79.2</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="1"/>
+        <v>1528.04</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>98</v>
+      </c>
+      <c r="M43">
+        <v>35</v>
+      </c>
+      <c r="N43">
+        <v>82</v>
+      </c>
+      <c r="P43">
+        <v>1492</v>
+      </c>
+      <c r="Q43">
+        <v>1545</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="0"/>
+        <v>81.06</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="1"/>
+        <v>1543.94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7714E7A8-D38C-4D74-8F6C-0E5719445AE5}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.34998626667073579"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="21.26953125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="44.54296875" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="49.26953125" customWidth="1"/>
+    <col min="5" max="5" width="58.453125" customWidth="1"/>
+    <col min="6" max="6" width="63.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="25">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="25">
+        <v>2014</v>
+      </c>
+      <c r="D2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="25">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="25">
+        <v>2016</v>
+      </c>
+      <c r="D3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="25">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="25">
+        <v>2020</v>
+      </c>
+      <c r="D4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="25">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="25">
+        <v>2022</v>
+      </c>
+      <c r="D5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="25">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="25">
+        <v>2021</v>
+      </c>
+      <c r="D6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="25">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="25">
+        <v>2018</v>
+      </c>
+      <c r="D7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="25">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="25">
+        <v>2015</v>
+      </c>
+      <c r="D8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{F030474D-2471-411D-A5DB-2465B50281A4}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{7581AE9F-10D7-47BB-9FC5-FBD56CC26639}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{22F06CAC-3534-4B3A-9B71-464A469D83E6}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{D56F411C-30EF-41FC-9CAE-88BC09391044}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{22F9CACC-4A72-499A-8058-F9C2F91522C3}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{69EF00AC-D000-4864-88A0-1F569DF528A6}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{409FB260-F32E-4257-9625-D3CC2ED2A465}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E5BCB7-B0F6-4E3B-8F08-5A1471634CD0}">
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
@@ -1898,8 +3572,8 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I2" s="12">
-        <f>AVERAGE(B2:H2)</f>
-        <v>0.97431121098722762</v>
+        <f>AVERAGE(Other!C10:C12)</f>
+        <v>1.4079277777797465</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1935,8 +3609,8 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I3" s="12">
-        <f t="shared" ref="I3:I13" si="1">AVERAGE(B3:H3)</f>
-        <v>1.8230835731315582</v>
+        <f>AVERAGE(Other!C4:C5)</f>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1968,12 +3642,12 @@
         <v>2.5</v>
       </c>
       <c r="H4" s="12">
-        <f t="shared" ref="H4:H13" si="2">H3</f>
+        <f t="shared" ref="H4:H13" si="1">H3</f>
         <v>1.639344262295082</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7660180492432396</v>
+        <f>$I$3</f>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1989,7 +3663,7 @@
         <v>1.4285714285714286</v>
       </c>
       <c r="D5" s="12">
-        <f t="shared" ref="D5:D13" si="3">D4</f>
+        <f t="shared" ref="D5:D13" si="2">D4</f>
         <v>3.2715420655938083</v>
       </c>
       <c r="E5" s="12">
@@ -2005,12 +3679,12 @@
         <v>2.5</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" si="1"/>
-        <v>1.8785131523706613</v>
+        <f t="shared" ref="I5:I13" si="3">$I$3</f>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2026,7 +3700,7 @@
         <v>1.2048192771084338</v>
       </c>
       <c r="D6" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E6" s="12">
@@ -2042,12 +3716,12 @@
         <v>2.5</v>
       </c>
       <c r="H6" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I6" s="12">
-        <f t="shared" si="1"/>
-        <v>1.8145839662383771</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2062,7 +3736,7 @@
         <v>1.05</v>
       </c>
       <c r="D7" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E7" s="12">
@@ -2078,12 +3752,12 @@
         <v>2.5</v>
       </c>
       <c r="H7" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I7" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7703498870645389</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2099,7 +3773,7 @@
         <v>1.2048192771084338</v>
       </c>
       <c r="D8" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E8" s="12">
@@ -2115,12 +3789,12 @@
         <v>2.5</v>
       </c>
       <c r="H8" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I8" s="12">
-        <f t="shared" si="1"/>
-        <v>1.8145839662383771</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2136,7 +3810,7 @@
         <v>1.2048192771084338</v>
       </c>
       <c r="D9" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E9" s="12">
@@ -2152,12 +3826,12 @@
         <v>2.5</v>
       </c>
       <c r="H9" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I9" s="12">
-        <f t="shared" si="1"/>
-        <v>1.8145839662383771</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2173,7 +3847,7 @@
         <v>1.2195121951219512</v>
       </c>
       <c r="D10" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E10" s="12">
@@ -2189,12 +3863,12 @@
         <v>2.5</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="1"/>
-        <v>1.818781942813668</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2210,7 +3884,7 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D11" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E11" s="12">
@@ -2226,12 +3900,12 @@
         <v>2.5</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7660180492432396</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2247,7 +3921,7 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D12" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E12" s="12">
@@ -2263,12 +3937,12 @@
         <v>2.5</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7660180492432396</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2284,7 +3958,7 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E13" s="12">
@@ -2300,12 +3974,12 @@
         <v>2.5</v>
       </c>
       <c r="H13" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.639344262295082</v>
       </c>
       <c r="I13" s="12">
-        <f t="shared" si="1"/>
-        <v>1.7660180492432396</v>
+        <f t="shared" si="3"/>
+        <v>3.2788295116156565</v>
       </c>
     </row>
     <row r="14" spans="1:9">

--- a/InputData/indst/SYIEUEFbIPaF/Start Year Indst Eqpt Unit E Factor by Indst Proc and Fuel.xlsx
+++ b/InputData/indst/SYIEUEFbIPaF/Start Year Indst Eqpt Unit E Factor by Indst Proc and Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\SYIEUEFbIPaF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583D8F56-BA9A-4554-A7B4-97607820984D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34034975-6E1C-4D32-8DFF-68B4A76338E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1520" windowWidth="17790" windowHeight="9120" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="12" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -23,18 +23,18 @@
     <sheet name="Cooling" sheetId="11" r:id="rId8"/>
     <sheet name="Electrochemical" sheetId="14" r:id="rId9"/>
     <sheet name="Other" sheetId="15" r:id="rId10"/>
-    <sheet name="References" sheetId="16" r:id="rId11"/>
-    <sheet name="SYIEUEFbIPaF" sheetId="2" r:id="rId12"/>
+    <sheet name="Lighting" sheetId="18" r:id="rId11"/>
+    <sheet name="References" sheetId="16" r:id="rId12"/>
+    <sheet name="SYIEUEFbIPaF" sheetId="2" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
     <externalReference r:id="rId15"/>
     <externalReference r:id="rId16"/>
   </externalReferences>
   <definedNames>
     <definedName name="base.year">#REF!</definedName>
-    <definedName name="CH4_to_CO2e">'[2]Cross-Page Data'!$C$12</definedName>
+    <definedName name="CH4_to_CO2e">'[1]Cross-Page Data'!$C$12</definedName>
     <definedName name="CH4GWP">#REF!</definedName>
     <definedName name="coal.past">#REF!</definedName>
     <definedName name="Constants.Density.Diesel">#REF!</definedName>
@@ -74,7 +74,7 @@
     <definedName name="EF.NaturalGas.CO2">#REF!</definedName>
     <definedName name="EF.NaturalGas.N2O">#REF!</definedName>
     <definedName name="GBP">#REF!</definedName>
-    <definedName name="gigwatts_to_megawatts">[3]About!$A$31</definedName>
+    <definedName name="gigwatts_to_megawatts">[2]About!$A$31</definedName>
     <definedName name="growth.scenario">#REF!</definedName>
     <definedName name="GWP.CH4">#REF!</definedName>
     <definedName name="GWP.N2O">#REF!</definedName>
@@ -105,7 +105,7 @@
     <definedName name="IX.a.scenario">#REF!</definedName>
     <definedName name="MGBP">#REF!</definedName>
     <definedName name="Minesize.xv.b">#REF!</definedName>
-    <definedName name="N2O_to_CO2e">'[2]Cross-Page Data'!$C$13</definedName>
+    <definedName name="N2O_to_CO2e">'[1]Cross-Page Data'!$C$13</definedName>
     <definedName name="N2OGWP">#REF!</definedName>
     <definedName name="nuclear.past">#REF!</definedName>
     <definedName name="plantsize.I.b">#REF!</definedName>
@@ -180,7 +180,7 @@
     <definedName name="Unit.TWh">#REF!</definedName>
     <definedName name="Unit.W">#REF!</definedName>
     <definedName name="Unit.year">#REF!</definedName>
-    <definedName name="unit_conv">[4]About!$A$123</definedName>
+    <definedName name="unit_conv">[3]About!$A$123</definedName>
     <definedName name="USD_Bn">#REF!</definedName>
     <definedName name="USD_mn">#REF!</definedName>
     <definedName name="USD2012_">#REF!</definedName>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="269">
   <si>
     <t>Source:</t>
   </si>
@@ -337,9 +337,6 @@
   </si>
   <si>
     <t>Machine Drive</t>
-  </si>
-  <si>
-    <t>Electrochem</t>
   </si>
   <si>
     <t>Other process</t>
@@ -1052,6 +1049,69 @@
   </si>
   <si>
     <t>https://www.fueleconomy.gov/feg/atv-ev.shtml</t>
+  </si>
+  <si>
+    <t>Other nonprocess</t>
+  </si>
+  <si>
+    <t>Facility HVAC</t>
+  </si>
+  <si>
+    <t>Facility Lighting</t>
+  </si>
+  <si>
+    <t>COP:</t>
+  </si>
+  <si>
+    <t>for HVAC systems with lower temperature lift than in process uses</t>
+  </si>
+  <si>
+    <t>https://www.mordorintelligence.com/industry-reports/industrial-lighting-market</t>
+  </si>
+  <si>
+    <t>Industrial lighting market</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>Fluorescent</t>
+  </si>
+  <si>
+    <t>HID fixtures</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>https://www.gelighting.com/inform/guide-energy-efficient-light-bulbs</t>
+  </si>
+  <si>
+    <t>Bulb efficiencies</t>
+  </si>
+  <si>
+    <t>Fluoresecent</t>
+  </si>
+  <si>
+    <t>Incandescent</t>
+  </si>
+  <si>
+    <t>HID</t>
+  </si>
+  <si>
+    <t>(assumption)</t>
+  </si>
+  <si>
+    <t>Avg intensity</t>
+  </si>
+  <si>
+    <t>Lighting is powered by electricity. To use other fuels one can use a generator</t>
+  </si>
+  <si>
+    <t>We assume a 35% generator efficiency.</t>
+  </si>
+  <si>
+    <t>Avg efficiency</t>
   </si>
 </sst>
 </file>
@@ -1810,42 +1870,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="About"/>
-      <sheetName val="EIA MECS Table 5.2"/>
-      <sheetName val="Med-High Temp Heat"/>
-      <sheetName val="Low Temp Heat"/>
-      <sheetName val="Cooling"/>
-      <sheetName val="Other"/>
-      <sheetName val="Efficiencies"/>
-      <sheetName val="Temperature Breakdown"/>
-      <sheetName val="References"/>
-      <sheetName val="Mapping"/>
-      <sheetName val="PIFURfE"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
       <sheetName val="Cross-Page Data"/>
@@ -1945,7 +1969,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -1982,7 +2006,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2361,9 +2385,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E490AE5-9E06-4EDB-8D15-DE332404A026}">
   <dimension ref="A1:B58"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="51.1796875" customWidth="1"/>
+    <col min="2" max="2" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2376,12 +2400,12 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2391,27 +2415,27 @@
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2421,27 +2445,27 @@
     </row>
     <row r="13" spans="1:2">
       <c r="B13" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="2:2">
@@ -2451,27 +2475,27 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="2:2">
@@ -2481,92 +2505,92 @@
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="B49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2616,18 +2640,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F2927FF-B932-47A4-981F-D26F3F21BFFF}">
   <dimension ref="A1:T43"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2647,7 +2671,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2657,30 +2681,30 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="C3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" t="s">
         <v>179</v>
       </c>
-      <c r="C3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>180</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>181</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>182</v>
-      </c>
-      <c r="H3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B4" s="27">
         <v>0.30299999999999999</v>
@@ -2699,12 +2723,12 @@
         <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" s="27">
         <f>AVERAGE(0.35,0.305,0.266)</f>
@@ -2715,7 +2739,7 @@
         <v>3.2573289902280131</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E5">
         <v>2100</v>
@@ -2726,7 +2750,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
@@ -2736,18 +2760,18 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9">
         <f>AVERAGE(0.836,0.885,0.905)</f>
@@ -2758,7 +2782,7 @@
         <v>1.1424219345011424</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E9">
         <v>2600</v>
@@ -2769,7 +2793,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B10">
         <f>B9*(1-AVERAGE(0.1,0.15))</f>
@@ -2781,12 +2805,12 @@
       </c>
       <c r="D10" s="28"/>
       <c r="F10" s="28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B11">
         <f>1/C11</f>
@@ -2805,7 +2829,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12">
         <f>1/C12</f>
@@ -2822,7 +2846,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -2832,7 +2856,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B15" s="14">
         <f>(AVERAGE(C4:C5)-AVERAGE(C10:C12))/AVERAGE(C4:C5)</f>
@@ -2848,104 +2872,104 @@
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="8:8">
       <c r="H20" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
+        <v>197</v>
+      </c>
+      <c r="D33" t="s">
         <v>198</v>
-      </c>
-      <c r="D33" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" t="s">
         <v>200</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D34" t="s">
         <v>201</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>202</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>203</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>204</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>205</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>206</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>207</v>
       </c>
-      <c r="J34" t="s">
+      <c r="M34" t="s">
         <v>208</v>
       </c>
-      <c r="M34" t="s">
+      <c r="P34" t="s">
         <v>209</v>
       </c>
-      <c r="P34" t="s">
+      <c r="S34" t="s">
         <v>210</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
         <v>211</v>
-      </c>
-      <c r="T34" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" t="s">
         <v>213</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>214</v>
       </c>
-      <c r="C35" t="s">
+      <c r="J35" t="s">
         <v>215</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>216</v>
       </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>217</v>
       </c>
-      <c r="L35" t="s">
-        <v>218</v>
-      </c>
       <c r="M35" t="s">
+        <v>215</v>
+      </c>
+      <c r="N35" t="s">
         <v>216</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>217</v>
       </c>
-      <c r="O35" t="s">
-        <v>218</v>
-      </c>
       <c r="P35" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q35" t="s">
         <v>216</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>217</v>
-      </c>
-      <c r="R35" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" s="18">
         <f>AVERAGE(S36:S37)</f>
@@ -3056,7 +3080,7 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B38" s="18">
         <f>AVERAGE(S38:S40)</f>
@@ -3208,7 +3232,7 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B41" s="18">
         <f>AVERAGE(S41:S43)</f>
@@ -3330,39 +3354,194 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BCB7FB-3B4B-4107-81D7-C01090592FB5}">
+  <dimension ref="A2:C24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="C4" s="14"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="C5" s="14"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6">
+        <v>0.20050000000000001</v>
+      </c>
+      <c r="C6" s="14"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="17">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" s="11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>268</v>
+      </c>
+      <c r="B16" s="11">
+        <f>B11*B4+B12*B5+B6*B14+B11*B7</f>
+        <v>0.85307500000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="11">
+        <f>1/B16</f>
+        <v>1.1722298742783459</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="11">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>268</v>
+      </c>
+      <c r="B23" s="11">
+        <f>B16*A21</f>
+        <v>0.29857624999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>265</v>
+      </c>
+      <c r="B24">
+        <f>1/B23</f>
+        <v>3.3492282122238457</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7714E7A8-D38C-4D74-8F6C-0E5719445AE5}">
   <sheetPr>
     <tabColor theme="1" tint="0.34998626667073579"/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.26953125" style="25" customWidth="1"/>
-    <col min="2" max="2" width="44.54296875" customWidth="1"/>
-    <col min="3" max="3" width="16.54296875" style="25" customWidth="1"/>
-    <col min="4" max="4" width="49.26953125" customWidth="1"/>
-    <col min="5" max="5" width="58.453125" customWidth="1"/>
-    <col min="6" max="6" width="63.81640625" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="44.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="49.28515625" customWidth="1"/>
+    <col min="5" max="5" width="58.42578125" customWidth="1"/>
+    <col min="6" max="6" width="63.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>226</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3370,16 +3549,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C2" s="25">
         <v>2014</v>
       </c>
       <c r="D2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>229</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3387,16 +3566,16 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C3" s="25">
         <v>2016</v>
       </c>
       <c r="D3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E3" s="16" t="s">
         <v>232</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3404,16 +3583,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C4" s="25">
         <v>2020</v>
       </c>
       <c r="D4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>235</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3421,16 +3600,16 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C5" s="25">
         <v>2022</v>
       </c>
       <c r="D5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>238</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3438,16 +3617,16 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C6" s="25">
         <v>2021</v>
       </c>
       <c r="D6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>241</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3455,16 +3634,16 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C7" s="25">
         <v>2018</v>
       </c>
       <c r="D7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3472,16 +3651,16 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C8" s="25">
         <v>2015</v>
       </c>
       <c r="D8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>247</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3498,19 +3677,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E5BCB7-B0F6-4E3B-8F08-5A1471634CD0}">
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="14.81640625" customWidth="1"/>
+    <col min="2" max="13" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -3536,10 +3715,16 @@
         <v>26</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>249</v>
+      </c>
+      <c r="J1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3572,11 +3757,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I2" s="12">
+        <f>'Heat pumps'!C28</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J2" s="12">
+        <f>Lighting!B17</f>
+        <v>1.1722298742783459</v>
+      </c>
+      <c r="K2" s="12">
         <f>AVERAGE(Other!C10:C12)</f>
         <v>1.4079277777797465</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3609,11 +3802,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I3" s="12">
+        <f>B3</f>
+        <v>1.2345679012345678</v>
+      </c>
+      <c r="J3" s="12">
+        <f>Lighting!B24</f>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K3" s="12">
         <f>AVERAGE(Other!C4:C5)</f>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3646,11 +3847,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I4" s="12">
-        <f>$I$3</f>
+        <f t="shared" ref="I4:I13" si="2">B4</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="J4" s="12">
+        <f>$J$3</f>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K4" s="12">
+        <f>$K$3</f>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3663,7 +3872,7 @@
         <v>1.4285714285714286</v>
       </c>
       <c r="D5" s="12">
-        <f t="shared" ref="D5:D13" si="2">D4</f>
+        <f t="shared" ref="D5:D13" si="3">D4</f>
         <v>3.2715420655938083</v>
       </c>
       <c r="E5" s="12">
@@ -3683,11 +3892,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I5" s="12">
-        <f t="shared" ref="I5:I13" si="3">$I$3</f>
+        <f t="shared" si="2"/>
+        <v>1.4285714285714286</v>
+      </c>
+      <c r="J5" s="12">
+        <f t="shared" ref="J5:J13" si="4">$J$3</f>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K5" s="12">
+        <f t="shared" ref="K5:K13" si="5">$K$3</f>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -3700,11 +3917,11 @@
         <v>1.2048192771084338</v>
       </c>
       <c r="D6" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E6" s="12">
-        <f t="shared" ref="E6:E10" si="4">$E$3</f>
+        <f t="shared" ref="E6:E10" si="6">$E$3</f>
         <v>1.9841269841269842</v>
       </c>
       <c r="F6" s="12">
@@ -3720,11 +3937,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I6" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.2048192771084338</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K6" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3736,11 +3961,11 @@
         <v>1.05</v>
       </c>
       <c r="D7" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E7" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.9841269841269842</v>
       </c>
       <c r="F7" s="12">
@@ -3756,11 +3981,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I7" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.05</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K7" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3773,11 +4006,11 @@
         <v>1.2048192771084338</v>
       </c>
       <c r="D8" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E8" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.9841269841269842</v>
       </c>
       <c r="F8" s="12">
@@ -3793,11 +4026,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I8" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.2048192771084338</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K8" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3810,11 +4051,11 @@
         <v>1.2048192771084338</v>
       </c>
       <c r="D9" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E9" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.9841269841269842</v>
       </c>
       <c r="F9" s="12">
@@ -3830,11 +4071,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I9" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.2048192771084338</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K9" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3847,11 +4096,11 @@
         <v>1.2195121951219512</v>
       </c>
       <c r="D10" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E10" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.9841269841269842</v>
       </c>
       <c r="F10" s="12">
@@ -3867,11 +4116,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.2195121951219512</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3884,7 +4141,7 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D11" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E11" s="12">
@@ -3904,13 +4161,21 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I11" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K11" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12">
         <f>Boilers!D17</f>
@@ -3921,11 +4186,11 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D12" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E12" s="12">
-        <f t="shared" ref="E12:E13" si="5">$E$4</f>
+        <f t="shared" ref="E12:E13" si="7">$E$4</f>
         <v>1.3871374527112232</v>
       </c>
       <c r="F12" s="12">
@@ -3941,13 +4206,21 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I12" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K12" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="12">
         <f>Boilers!D17</f>
@@ -3958,11 +4231,11 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D13" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2715420655938083</v>
       </c>
       <c r="E13" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.3871374527112232</v>
       </c>
       <c r="F13" s="12">
@@ -3978,11 +4251,19 @@
         <v>1.639344262295082</v>
       </c>
       <c r="I13" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="4"/>
+        <v>3.3492282122238457</v>
+      </c>
+      <c r="K13" s="12">
+        <f t="shared" si="5"/>
         <v>3.2788295116156565</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:11">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -3991,6 +4272,8 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4000,26 +4283,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{208DE7CD-1195-47A7-9F7A-06312F92713C}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="D18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s">
         <v>43</v>
-      </c>
-      <c r="E18" t="s">
-        <v>44</v>
       </c>
       <c r="F18">
         <v>2018</v>
@@ -4028,27 +4311,27 @@
         <v>2050</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
         <v>46</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>47</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>48</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>49</v>
       </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19">
         <v>2021</v>
@@ -4057,18 +4340,18 @@
         <v>2050</v>
       </c>
       <c r="K19" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" t="s">
         <v>51</v>
-      </c>
-      <c r="M19" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" t="s">
         <v>53</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
       </c>
       <c r="D20">
         <v>0.218</v>
@@ -4101,10 +4384,10 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <v>2.1999999999999999E-2</v>
@@ -4137,10 +4420,10 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22">
         <v>0.20399999999999999</v>
@@ -4173,10 +4456,10 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23">
         <v>3.9E-2</v>
@@ -4209,10 +4492,10 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>1.2999999999999999E-2</v>
@@ -4245,10 +4528,10 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25">
         <v>0.19900000000000001</v>
@@ -4281,10 +4564,10 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26">
         <v>1E-3</v>
@@ -4317,10 +4600,10 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D27">
         <v>1.0999999999999999E-2</v>
@@ -4353,10 +4636,10 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28">
         <v>7.0000000000000001E-3</v>
@@ -4396,52 +4679,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01E6737B-14AA-41CE-9388-6419CF592696}">
   <dimension ref="H2:O36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="8" max="8" width="14.7265625" customWidth="1"/>
-    <col min="9" max="9" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.1796875" customWidth="1"/>
-    <col min="11" max="11" width="30.7265625" customWidth="1"/>
-    <col min="12" max="12" width="22.1796875" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" customWidth="1"/>
+    <col min="11" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" customWidth="1"/>
     <col min="13" max="13" width="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.1796875" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="8:15">
       <c r="H2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="8:15">
       <c r="H3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="8:15" s="9" customFormat="1" ht="45">
+      <c r="I4" s="9" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="8:15" s="9" customFormat="1" ht="43.5">
-      <c r="I4" s="9" t="s">
-        <v>90</v>
-      </c>
       <c r="J4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="L4" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="8:15">
       <c r="L5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="8:15">
       <c r="I6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J6">
         <v>83</v>
@@ -4450,7 +4733,7 @@
         <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M6">
         <v>90.1</v>
@@ -4465,7 +4748,7 @@
     </row>
     <row r="7" spans="8:15">
       <c r="I7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J7">
         <v>89</v>
@@ -4474,7 +4757,7 @@
         <v>89</v>
       </c>
       <c r="L7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M7">
         <v>93.1</v>
@@ -4489,7 +4772,7 @@
     </row>
     <row r="8" spans="8:15">
       <c r="I8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J8">
         <v>92</v>
@@ -4498,7 +4781,7 @@
         <v>91</v>
       </c>
       <c r="L8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M8">
         <v>94.7</v>
@@ -4513,7 +4796,7 @@
     </row>
     <row r="9" spans="8:15">
       <c r="I9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J9">
         <v>93</v>
@@ -4522,7 +4805,7 @@
         <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M9">
         <v>95.9</v>
@@ -4537,7 +4820,7 @@
     </row>
     <row r="10" spans="8:15">
       <c r="I10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10">
         <v>93</v>
@@ -4546,7 +4829,7 @@
         <v>93</v>
       </c>
       <c r="L10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M10">
         <v>96.2</v>
@@ -4561,7 +4844,7 @@
     </row>
     <row r="11" spans="8:15">
       <c r="I11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J11">
         <v>93</v>
@@ -4570,7 +4853,7 @@
         <v>94</v>
       </c>
       <c r="L11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M11">
         <v>96.2</v>
@@ -4585,7 +4868,7 @@
     </row>
     <row r="12" spans="8:15">
       <c r="I12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J12">
         <v>93</v>
@@ -4604,7 +4887,7 @@
     </row>
     <row r="13" spans="8:15">
       <c r="I13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J13">
         <v>92</v>
@@ -4623,7 +4906,7 @@
     </row>
     <row r="14" spans="8:15">
       <c r="I14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J14">
         <v>86</v>
@@ -4642,13 +4925,13 @@
     </row>
     <row r="15" spans="8:15">
       <c r="I15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J15">
         <v>91</v>
       </c>
       <c r="K15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <f>M14</f>
@@ -4661,23 +4944,23 @@
     </row>
     <row r="17" spans="9:12">
       <c r="J17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="9:12">
       <c r="I18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J18" s="18">
         <v>25.980397752045299</v>
       </c>
       <c r="L18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="9:12">
       <c r="I19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J19" s="18">
         <v>67.647063795395397</v>
@@ -4688,18 +4971,18 @@
     </row>
     <row r="20" spans="9:12">
       <c r="I20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J20" s="18">
         <v>86.928108261286297</v>
       </c>
       <c r="L20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="9:12">
       <c r="I21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J21" s="18">
         <v>71.895427750300499</v>
@@ -4707,7 +4990,7 @@
     </row>
     <row r="22" spans="9:12">
       <c r="I22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="18">
         <v>64.379085998847998</v>
@@ -4715,7 +4998,7 @@
     </row>
     <row r="23" spans="9:12">
       <c r="I23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J23" s="18">
         <v>94.281049327759803</v>
@@ -4723,7 +5006,7 @@
     </row>
     <row r="24" spans="9:12">
       <c r="I24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J24" s="18">
         <v>62.908497785553301</v>
@@ -4731,7 +5014,7 @@
     </row>
     <row r="25" spans="9:12">
       <c r="I25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J25" s="18">
         <v>34.803927031813501</v>
@@ -4739,7 +5022,7 @@
     </row>
     <row r="26" spans="9:12">
       <c r="I26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J26" s="18">
         <v>17.6470525756977</v>
@@ -4747,7 +5030,7 @@
     </row>
     <row r="27" spans="9:12">
       <c r="I27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J27" s="18">
         <v>17.156856504599499</v>
@@ -4755,10 +5038,10 @@
     </row>
     <row r="29" spans="9:12">
       <c r="J29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="30" spans="9:12">
@@ -4783,7 +5066,7 @@
     </row>
     <row r="34" spans="10:11">
       <c r="J34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="10:11">
@@ -4806,27 +5089,47 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6325B5-8F49-4EFF-9AFE-787745135977}">
-  <dimension ref="B24:D25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B24:D28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="24" spans="2:4">
       <c r="B24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="2:4">
       <c r="B25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25">
         <f>1/C24</f>
         <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C27">
+        <v>3.5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28">
+        <f>1/C27</f>
+        <v>0.2857142857142857</v>
       </c>
     </row>
   </sheetData>
@@ -4838,10 +5141,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A620FBB6-6DA6-4445-A3B7-9FDC2FA0643B}">
   <dimension ref="B2:D23"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="61.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -4860,15 +5163,15 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
         <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17">
         <v>0.75</v>
@@ -4880,7 +5183,7 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18">
         <v>0.81</v>
@@ -4892,7 +5195,7 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19">
         <v>0.82</v>
@@ -4904,7 +5207,7 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20">
         <v>0.83</v>
@@ -4916,7 +5219,7 @@
     </row>
     <row r="21" spans="2:4">
       <c r="B21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21">
         <v>0.83</v>
@@ -4928,7 +5231,7 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22">
         <v>0.7</v>
@@ -4940,7 +5243,7 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23">
         <v>0.7</v>
@@ -4959,39 +5262,39 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1A33F7-3B58-415B-8180-0D752D7B0DBE}">
   <dimension ref="I3:O15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
     <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="9:15">
       <c r="I3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="9:15">
       <c r="I4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" t="s">
         <v>82</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>83</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>84</v>
-      </c>
-      <c r="O4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="5" spans="9:15">
       <c r="I5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J5" s="17">
         <v>0.27800000000000002</v>
@@ -5001,7 +5304,7 @@
         <v>0.5</v>
       </c>
       <c r="M5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N5" s="11">
         <f>SUMPRODUCT(J5:J8,K5:K8)/SUM(J5:J8)</f>
@@ -5014,7 +5317,7 @@
     </row>
     <row r="6" spans="9:15">
       <c r="I6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J6" s="14">
         <f>SUM(12.1%,31.8%)</f>
@@ -5025,7 +5328,7 @@
         <v>0.65</v>
       </c>
       <c r="M6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N6" s="11">
         <f>SUMPRODUCT(J12:J15,K12:K15)/SUM(J12:J15)</f>
@@ -5038,7 +5341,7 @@
     </row>
     <row r="7" spans="9:15">
       <c r="I7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J7" s="17">
         <v>4.7E-2</v>
@@ -5050,7 +5353,7 @@
     </row>
     <row r="8" spans="9:15">
       <c r="I8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J8" s="17">
         <v>3.9E-2</v>
@@ -5062,23 +5365,23 @@
     </row>
     <row r="10" spans="9:15">
       <c r="I10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="9:15">
       <c r="I11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" t="s">
         <v>82</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="12" spans="9:15">
       <c r="I12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J12" s="17">
         <v>0.27800000000000002</v>
@@ -5090,7 +5393,7 @@
     </row>
     <row r="13" spans="9:15">
       <c r="I13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J13" s="14">
         <f>SUM(12.1%,31.8%)</f>
@@ -5103,7 +5406,7 @@
     </row>
     <row r="14" spans="9:15">
       <c r="I14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J14" s="17">
         <v>4.7E-2</v>
@@ -5115,7 +5418,7 @@
     </row>
     <row r="15" spans="9:15">
       <c r="I15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J15" s="17">
         <v>3.9E-2</v>
@@ -5134,11 +5437,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCE2796E-BC60-4177-9FEB-8E9F5425DFFA}">
   <dimension ref="A2:I21"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:9">
       <c r="A2" s="22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -5151,24 +5454,24 @@
     </row>
     <row r="3" spans="1:9">
       <c r="B3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4">
         <v>425</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E4">
         <f>AVERAGE(B4:B6)</f>
@@ -5181,32 +5484,32 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B5">
         <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B6">
         <v>400</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G7">
         <f>1/G4</f>
@@ -5215,13 +5518,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B8">
         <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E8">
         <f>AVERAGE(B8:B9)</f>
@@ -5230,18 +5533,18 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B9">
         <v>300</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
@@ -5254,23 +5557,23 @@
     </row>
     <row r="12" spans="1:9">
       <c r="B12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" s="23">
         <v>0.504</v>
       </c>
       <c r="G13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G14">
         <f>1/B13</f>
@@ -5279,7 +5582,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="23">
         <v>0.55100000000000005</v>
@@ -5287,7 +5590,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="22" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -5300,10 +5603,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="B18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -5311,7 +5614,7 @@
         <v>1100</v>
       </c>
       <c r="C19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G19">
         <f>B21/B19</f>
@@ -5320,10 +5623,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="B20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -5331,7 +5634,7 @@
         <v>793</v>
       </c>
       <c r="C21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G21">
         <f>1/G19</f>
@@ -5346,22 +5649,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9BDABE4-2D06-45EB-ACBA-FE104E27935D}">
   <dimension ref="B2:N32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="2:11">
       <c r="J3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="2:11">
@@ -5409,39 +5712,39 @@
     </row>
     <row r="18" spans="2:14">
       <c r="B18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="2:14">
       <c r="I21" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="J23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L23" t="s">
         <v>141</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>142</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>143</v>
-      </c>
-      <c r="N23" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="J24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K24">
         <v>0.79</v>
@@ -5461,7 +5764,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="J25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K25">
         <v>0.79</v>
@@ -5473,7 +5776,7 @@
     </row>
     <row r="26" spans="2:14">
       <c r="J26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K26">
         <v>0.71699999999999997</v>
@@ -5485,7 +5788,7 @@
     </row>
     <row r="27" spans="2:14">
       <c r="J27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K27">
         <v>0.63900000000000001</v>
@@ -5497,12 +5800,12 @@
     </row>
     <row r="28" spans="2:14">
       <c r="J28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="J29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K29">
         <v>0.70299999999999996</v>
@@ -5514,7 +5817,7 @@
     </row>
     <row r="30" spans="2:14">
       <c r="J30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K30">
         <v>0.63400000000000001</v>
@@ -5526,7 +5829,7 @@
     </row>
     <row r="31" spans="2:14">
       <c r="J31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K31">
         <v>0.57599999999999996</v>
@@ -5538,7 +5841,7 @@
     </row>
     <row r="32" spans="2:14">
       <c r="J32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K32">
         <v>0.57599999999999996</v>
@@ -5557,16 +5860,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74BF9617-11C7-43F5-9981-C4D048784240}">
   <dimension ref="A2:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3" s="11">
         <v>0.61</v>
@@ -5574,12 +5877,12 @@
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B5" s="11">
         <v>0.7</v>
@@ -5587,12 +5890,12 @@
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B8" s="11">
         <v>0.61</v>
@@ -5600,12 +5903,12 @@
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B10" s="11">
         <v>0.72</v>
@@ -5613,7 +5916,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" s="11">
         <f>AVERAGE(B8,B3)</f>
@@ -5622,7 +5925,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B13">
         <f>1/B12</f>
